--- a/docs/EAA_Viec_phai_lam.xlsx
+++ b/docs/EAA_Viec_phai_lam.xlsx
@@ -72,11 +72,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
@@ -88,6 +83,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -152,22 +152,19 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -911,12 +908,12 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Bảng 12 dòng cho Chương 3, kèm danh sách lỗi bộ dò BỎ SÓT</t>
+          <t>ĐÃ ĐO: bắt được 3/13 · trúng một phần 1 · kêu trật 7 · BỎ SÓT 0. Và contract kêu sớm hơn người 54 phút ở ca imu_start_read</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Cần một bài canh để bảng không cũ đi khi lịch sử dài thêm</t>
+          <t>TC-146 (8 bài) — canh cả việc chân lý nền KHÔNG bị sửa sau khi chốt</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -939,9 +936,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr">
-        <is>
-          <t>ĐANG LÀM</t>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>XONG (SL-179)</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1003,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
@@ -1073,7 +1070,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
@@ -1140,7 +1137,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="M7" s="11" t="inlineStr">
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
@@ -1207,7 +1204,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="M8" s="11" t="inlineStr">
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
@@ -1274,7 +1271,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="M9" s="11" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
@@ -1341,7 +1338,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
@@ -1408,7 +1405,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="M11" s="12" t="inlineStr">
+      <c r="M11" s="11" t="inlineStr">
         <is>
           <t>CHỜ NGƯỜI</t>
         </is>
@@ -1475,7 +1472,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="M12" s="11" t="inlineStr">
+      <c r="M12" s="10" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
@@ -1542,7 +1539,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="M13" s="11" t="inlineStr">
+      <c r="M13" s="10" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
@@ -1609,7 +1606,7 @@
           <t>13</t>
         </is>
       </c>
-      <c r="M14" s="11" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
@@ -1676,7 +1673,7 @@
           <t>14</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
@@ -1737,14 +1734,14 @@
           <t>SC-01</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>ĐO</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>3 trên 12 lần từ chối tại G3 là mã TỰ CHỈNH CHO VỪA ĐỒ ĐO của chính nó, và cả ba qua sạch bốn cổng máy. Ghi ngày 03/09, trước khi bộ dò nào tồn tại</t>
+          <t>3 trên 12 lần từ chối tại G3 (đếm lại nhật ký được 13 — xem SL-179) là mã TỰ CHỈNH CHO VỪA ĐỒ ĐO của chính nó, và cả ba qua sạch bốn cổng máy. Ghi ngày 03/09, trước khi bộ dò nào tồn tại</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -1764,7 +1761,7 @@
           <t>SC-02</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>ĐO</t>
         </is>
@@ -1791,7 +1788,7 @@
           <t>SC-03</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>ĐO</t>
         </is>
@@ -1818,7 +1815,7 @@
           <t>SC-04</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>ĐO</t>
         </is>
@@ -1845,7 +1842,7 @@
           <t>SC-05</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>VĂN LIỆU</t>
         </is>
@@ -1872,7 +1869,7 @@
           <t>SC-06</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>SỔ SAI LỆCH</t>
         </is>
@@ -1899,7 +1896,7 @@
           <t>SC-07</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>ĐO</t>
         </is>
@@ -1926,7 +1923,7 @@
           <t>SC-08</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>KHAI (đối thủ)</t>
         </is>
@@ -1953,7 +1950,7 @@
           <t>SC-09</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>ĐO</t>
         </is>
@@ -1980,7 +1977,7 @@
           <t>SC-10</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>ĐO</t>
         </is>
@@ -2007,7 +2004,7 @@
           <t>SC-11</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>SỔ SAI LỆCH</t>
         </is>
@@ -2034,7 +2031,7 @@
           <t>SC-12</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>KHAI (đối thủ)</t>
         </is>
@@ -2061,7 +2058,7 @@
           <t>SC-13</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>ĐO</t>
         </is>
@@ -2088,7 +2085,7 @@
           <t>SC-14</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>ĐO</t>
         </is>
@@ -2115,7 +2112,7 @@
           <t>SC-15</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>SUY RA</t>
         </is>
@@ -2142,7 +2139,7 @@
           <t>SC-16</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>SUY RA</t>
         </is>
@@ -2169,7 +2166,7 @@
           <t>SC-17</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>ĐO</t>
         </is>
@@ -2196,7 +2193,7 @@
           <t>SC-18</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>ĐO</t>
         </is>
@@ -2261,7 +2258,7 @@
       </c>
     </row>
     <row r="2" ht="68" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Embedder</t>
         </is>
@@ -2283,7 +2280,7 @@
       </c>
     </row>
     <row r="3" ht="68" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Skilled AI Agents (arXiv 2603.19583)</t>
         </is>
@@ -2305,7 +2302,7 @@
       </c>
     </row>
     <row r="4" ht="68" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>STM32 Sidekick · MCP Espressif</t>
         </is>
@@ -2327,7 +2324,7 @@
       </c>
     </row>
     <row r="5" ht="68" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Parasoft · LDRA · QA Systems</t>
         </is>
@@ -2379,7 +2376,7 @@
       </c>
     </row>
     <row r="2" ht="50" customHeight="1">
-      <c r="A2" s="19" t="n">
+      <c r="A2" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -2389,7 +2386,7 @@
       </c>
     </row>
     <row r="3" ht="50" customHeight="1">
-      <c r="A3" s="19" t="n">
+      <c r="A3" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -2399,7 +2396,7 @@
       </c>
     </row>
     <row r="4" ht="50" customHeight="1">
-      <c r="A4" s="19" t="n">
+      <c r="A4" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2409,7 +2406,7 @@
       </c>
     </row>
     <row r="5" ht="50" customHeight="1">
-      <c r="A5" s="19" t="n">
+      <c r="A5" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -2419,7 +2416,7 @@
       </c>
     </row>
     <row r="6" ht="50" customHeight="1">
-      <c r="A6" s="19" t="n">
+      <c r="A6" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2429,7 +2426,7 @@
       </c>
     </row>
     <row r="7" ht="50" customHeight="1">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="6" t="inlineStr">

--- a/docs/EAA_Viec_phai_lam.xlsx
+++ b/docs/EAA_Viec_phai_lam.xlsx
@@ -936,7 +936,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>XONG (SL-179)</t>
         </is>

--- a/docs/EAA_Viec_phai_lam.xlsx
+++ b/docs/EAA_Viec_phai_lam.xlsx
@@ -970,22 +970,22 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>eaa/skills.py (mới) · eaa/composer.py · packs/*/</t>
+          <t>eaa/procedure.py · eaa/composer.py · packs/avr/procedures/ · projects/*/procedures/</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>So pass@k TRƯỚC và SAU khi bật lớp kỹ năng, trên cùng bộ nhiệm vụ V2</t>
+          <t>So pass@k TRƯỚC và SAU khi bật lớp thủ tục, trên cùng bộ nhiệm vụ V2. CƠ CHẾ ĐÃ XONG; con số CHƯA ĐO ĐƯỢC</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>TC-139 (đã đặt chỗ trong kế hoạch, chưa viết)</t>
+          <t>TC-139 (21 bài, 5 đột biến đều bị bắt) — canh cơ chế; con số ablation vẫn chờ V2</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>V2 — không có bộ nhiệm vụ thì không so được trước/sau</t>
+          <t>V2 — cơ chế đã có (SL-180), nhưng không có bộ nhiệm vụ thì không so được trước/sau</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
@@ -1003,9 +1003,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>XONG CƠ CHẾ — số chờ V2</t>
         </is>
       </c>
     </row>
